--- a/practice/answers/s1_q28.xlsx
+++ b/practice/answers/s1_q28.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -51,15 +50,15 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="0024302A"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="002F5D46"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -97,7 +96,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -107,25 +106,22 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -494,27 +490,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>A blended application rate</t>
+          <t>What Excel does to data on the way in</t>
         </is>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total pounds over total acres. The plain average of the four rates sits higher because the heaviest rates are on the smallest fields.</t>
+          <t>Typed into a General column, three of these variety codes become dates and every RM ID loses its leading zeros. Setting the column to Text first stops it.</t>
         </is>
       </c>
     </row>
@@ -522,188 +519,189 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>As typed (ID)</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Acres</t>
+          <t>As typed (Variety)</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Rate (lb/ac)</t>
+          <t>Yield</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Pounds</t>
+          <t>ID in a General column</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>The formula in D</t>
+          <t>Variety in a General column</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Field 1</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>86</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D5" s="8">
-        <f>B5*C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="9">
-        <f>_xlfn.FORMULATEXT(D5)</f>
-        <v/>
+          <t>00127</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>SEPT1</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <v>127</v>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>1-Sep</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Field 2</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>142</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="D6" s="8">
-        <f>B6*C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="9">
-        <f>_xlfn.FORMULATEXT(D6)</f>
-        <v/>
+          <t>00308</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>AAC2</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>308</v>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>AAC2</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Field 3</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>64</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D7" s="8">
-        <f>B7*C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="9">
-        <f>_xlfn.FORMULATEXT(D7)</f>
-        <v/>
+          <t>01045</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>MAR2</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1045</v>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>2-Mar</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Field 4</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>119</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D8" s="8">
-        <f>B8*C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="9">
-        <f>_xlfn.FORMULATEXT(D8)</f>
-        <v/>
+          <t>00276</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>BW945</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>276</v>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>BW945</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B9" s="11">
-        <f>SUM(B5:B8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="12">
-        <f>SUM(D5:D8)</f>
-        <v/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>00519</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>519</v>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>3-Jan</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1"/>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Blended: pounds / acres</t>
-        </is>
-      </c>
-      <c r="C11" s="13">
-        <f>D9/B9</f>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Mean yield</t>
+        </is>
+      </c>
+      <c r="C11" s="10">
+        <f>AVERAGE(C5:C9)</f>
         <v/>
       </c>
-      <c r="E11" s="9">
+      <c r="F11" s="11">
         <f>_xlfn.FORMULATEXT(C11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Blended: SUMPRODUCT</t>
-        </is>
-      </c>
-      <c r="C12" s="13">
-        <f>SUMPRODUCT(B5:B8,C5:C8)/SUM(B5:B8)</f>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C12" s="12">
+        <f>COUNT(C5:C9)</f>
         <v/>
       </c>
-      <c r="E12" s="9">
+      <c r="F12" s="11">
         <f>_xlfn.FORMULATEXT(C12)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>AVERAGE of the rate column</t>
-        </is>
-      </c>
-      <c r="C13" s="13">
-        <f>AVERAGE(C5:C8)</f>
-        <v/>
-      </c>
-      <c r="E13" s="9">
-        <f>_xlfn.FORMULATEXT(C13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1"/>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>3.28 lb/ac blended against a plain average of 3.40. Order on the total -- 1,347.4 lb -- because that is the amount of product the farm actually needs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1"/>
+    <row r="13" ht="18" customHeight="1"/>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Columns A and B are formatted as Text, which is why they still read as typed. Columns D and E show what a General column does with the same entries: the IDs become numbers and lose their zeros, and SEPT1, MAR2 and 1-3 become dates. The yields are untouched throughout -- the numbers are right and the sheet is still wrong, because nothing can be matched back to the RM it came from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A14:F14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/practice/answers/s1_q28.xlsx
+++ b/practice/answers/s1_q28.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +16,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="D-MMM"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,45 +30,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -75,12 +42,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,35 +78,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,218 +472,355 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="3" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>What Excel does to data on the way in</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Typed into a General column, three of these variety codes become dates and every RM ID loses its leading zeros. Setting the column to Text first stops it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>As typed (ID)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>As typed (Variety)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Yield</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>ID in a General column</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Variety in a General column</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+          <t>RM ID (General)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Variety (General)</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Yield (bu/ac)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>RM ID (Text)</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Variety (Text)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>127</v>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>00127</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>SEPT1</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>308</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>AAC2</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>38.6</v>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>00308</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>AAC2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>1045</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>46083</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>01045</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>MAR2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>276</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>BW945</t>
+        </is>
+      </c>
       <c r="C5" s="6" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>127</v>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>1-Sep</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>00308</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>AAC2</t>
-        </is>
+        <v>36.1</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>00276</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>BW945</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>519</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>46025</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>308</v>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>AAC2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>01045</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>MAR2</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>1045</v>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>2-Mar</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>00276</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>BW945</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>276</v>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>BW945</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+        <v>39.9</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>00519</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>519</v>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>3-Jan</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1"/>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Mean yield</t>
         </is>
       </c>
-      <c r="C11" s="10">
-        <f>AVERAGE(C5:C9)</f>
+      <c r="B8" s="9">
+        <f>AVERAGE(C2:C6)</f>
         <v/>
       </c>
-      <c r="F11" s="11">
-        <f>_xlfn.FORMULATEXT(C11)</f>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="B9" s="8">
+        <f>COUNT(C2:C6)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C12" s="12">
-        <f>COUNT(C5:C9)</f>
-        <v/>
-      </c>
-      <c r="F12" s="11">
-        <f>_xlfn.FORMULATEXT(C12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1"/>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Columns A and B are formatted as Text, which is why they still read as typed. Columns D and E show what a General column does with the same entries: the IDs become numbers and lose their zeros, and SEPT1, MAR2 and 1-3 become dates. The yields are untouched throughout -- the numbers are right and the sheet is still wrong, because nothing can be matched back to the RM it came from.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1"/>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Under General format the RM IDs come back as the numbers 127, 308, 1045, 276, 519, and SEPT1, MAR2 and 1-3 come back as the dates 1-Sep, 2-Mar and 3-Jan. AAC2 and BW945 survive.</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Excel reads a leading-zero string as a number and drops the zeros, because to a number they carry no value. It reads SEPT1, MAR2 and 1-3 as abbreviated dates. Each guess is reasonable in isolation and wrong here.</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="n"/>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="12" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="n"/>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>With the columns formatted as Text before typing, all five IDs and all five variety codes come back exactly as typed -- setting the type before the data arrives prevents the guess.</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n"/>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="14" t="n"/>
+      <c r="E18" s="14" t="n"/>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="14" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="14" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>An .xlsx file stores the type of every cell, so a workbook reopens holding what it held. A .csv is only text, with no type information, so Excel guesses afresh on every open -- and a file that has been opened, guessed at and saved has lost the original values. Importing via Data &gt; Get Data &gt; From Text/CSV lets the column types be set before anything is read.</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="16" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="16" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="16" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>The identifiers are what let a yield be matched to the right RM and the right variety; corrupt them and the numbers are accurate measurements of nothing you can name.</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n"/>
+      <c r="B27" s="8" t="n"/>
+      <c r="C27" s="8" t="n"/>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A14:F14"/>
+  <mergeCells count="5">
+    <mergeCell ref="A21:G24"/>
+    <mergeCell ref="A26:G27"/>
+    <mergeCell ref="A14:G16"/>
+    <mergeCell ref="A18:G19"/>
+    <mergeCell ref="A11:G12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
